--- a/신고신저가_20260824.xlsx
+++ b/신고신저가_20260824.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="164" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <color rgb="00C00000"/>
     </font>
@@ -76,18 +77,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -453,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -611,7 +616,84 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>💬 ■ 결론: 금요일 시장을 관통한 것은 미 재무부의 장기국채 바이백 확대와 국가부채 40조달러 돌파였다. 달러가 밀리고 금이 3개월래 최고인 온스당 4,608달러로 올라서면서 금·구리 광산주가 미국과 중화권에서 동시에 신고가를 냈고, 같은 힘이 반대편에서는 장기금리를 4.7%대에 붙들어 미국 규제 유틸리티 14종을 무더기 신저가로 밀어냈다. 지수는 조용했지만 그 아래에서는 실물자산과 채권 대용물이 정면으로 갈렸다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>■ 美(8/21): 지수의 소폭 상승은 내부에서 벌어진 자리바꿈을 가렸다. S&amp;P500과 나스닥이 나란히 0.43퍼센트 올랐는데, 섹터 수익률은 소재가 2.1퍼센트로 가장 앞서고 유틸리티가 2.3퍼센트 하락으로 홀로 처졌다. 신저가 32종 가운데 14종이 유틸리티였고 셈프라가 5.1퍼센트 빠지는 등 대형 규제 전력사가 예외 없이 밀렸다. 반대편에서는 프리포트맥모란과 서던코퍼가 구리 강세를 타고 8퍼센트 안팎 오르며 비에너지광물 15종을 신고가로 올려놨고, 소프트웨어를 포함한 기술서비스도 18종이 신고가를 찍었다. 다만 텍사스인스트루먼트와 온세미컨덕터를 포함한 전기·전자 7종은 나란히 신저가여서, 테크가 서비스와 하드웨어로 갈라져 움직였다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ 日(8/21): 닛케이가 0.3퍼센트 내리며 4개 시장 중 유일하게 약했지만, 해운은 따로 놀았다. 벌크 운임 반등을 타고 가와사키기선이 7.3퍼센트, 니혼유센이 4.5퍼센트 오르며 운수·물류가 업종 상위에 섰다. 반면 패스트리테일링이 3.6퍼센트 빠져 신저가로 내려앉았는데, 미국 대형 유통의 실적 부진이 소비주 심리로 옮겨붙은 결과로 보인다. 기계 업종이 3.0퍼센트 하락해 가장 부진했고, 다이킨공업의 신저가도 이달 초 분기 실적 부진의 여진이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>■ 홍콩(8/21): 항셍지수가 1.2퍼센트 오르며 이번 주 3.6퍼센트 상승으로 4개 시장 중 가장 강했고, 주도주는 명확히 광산이었다. 츠펑황금이 12.4퍼센트, 산둥황금이 8.7퍼센트 뛰며 금광주가 무더기로 신고가 행진을 이어갔고, 쯔진광업도 4.9퍼센트 올라 비에너지광물 5종이 모두 신고가였다. 신저가는 단 2종에 그쳐 시장 폭 자체가 건강했다. 눈에 띄는 예외는 팝마트로, 상반기 이익 성장 둔화를 시사하며 3.1퍼센트 하락해 홀로 신저가로 떨어졌다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>■ 中(8/21): 상해종합은 0.04퍼센트로 사실상 제자리였지만 업종 간 온도차는 컸다. 유색금속 상장지수펀드가 3.3퍼센트 올라 홍콩 금광주와 같은 재료를 공유했고, 국제유가가 한 달래 최고치로 반등하면서 페트로차이나와 헝이석화가 신고가를 냈다. 코스코해운홀딩스는 유럽항로 운임 급등을 타고 52주 고가를 새로 뚫었다. 약한 쪽은 미국과 같은 자리여서, 화능국제전력을 비롯한 전력 유틸리티가 신저가로 밀렸다. 8월 19일 상장한 휴머노이드 로봇업체 유니트리는 이틀 만에 차익매물이 나오며 2.1퍼센트 하락했다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>■ 체크: ① 미 10년물이 4.7퍼센트대에 고착되는지를 유틸리티 신저가 종목 수가 더 늘어나는지로 확인한다. ② 은이 8월 한 달에만 20퍼센트 올랐으므로 되돌림이 나올 때 광산주가 금속 가격보다 먼저 꺾이는지 본다. ③ 미국 테크가 서비스 강세와 하드웨어 약세로 갈라진 구도가 이어지는지, 반도체 신저가 종목이 늘어나는지 지켜본다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>■ 배울점: 금요일은 하나의 재료가 두 업종을 정반대로 움직인 교과서였다. 재료는 미 재무부가 장기국채 바이백을 두 배로 늘리고 국가부채가 40조달러를 넘어선 것이며, 여기서 갈라진 것은 통화 신뢰의 약화와 장기금리의 고착이다. 금광주로 가는 길은 이익 경로다. 금값이 오르면 광산업체는 판매단가만 오르고 채굴원가는 단기적으로 고정돼 있어 상승분이 거의 그대로 마진에 얹히는데, 이 지렛대 때문에 금값이 1.8퍼센트 오르는 동안 츠펑황금은 12.4퍼센트 뛰었다. 유틸리티로 가는 길은 멀티플 경로다. 규제 유틸리티는 요금이 규제로 묶여 이익이 거의 변하지 않으니 주가는 사실상 배당 흐름의 현재가치, 즉 채권 대용물로 거래되고, 장기금리가 오르면 이익은 그대로인데 할인율만 높아져 밸류가 깎인다. 선행 주가수익비율이 15~22배로 비싸지 않은데도 하루에 2~5퍼센트씩 빠진 이유가 여기 있는데, 싸서 방어되는 것이 아니라 금리에 대한 노출이 순수해서 그렇다. 이 해석이 맞는지는 다음 세션에 금리가 되밀릴 때 확인된다. 금리가 내리는데도 유틸리티가 반등하지 못한다면 원인은 금리가 아니라 다른 곳에 있다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>■ 참고: 한국시간 8월 24일 월요일 아침 실행이라 4개 시장 모두 직전 거래일인 8월 21일 금요일 마감분이다. 주말 공백이 끼어 미국 데이터는 약 2일 반 전 종가이며, 아시아 3개 시장은 오늘 장이 열리기 전 시점이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>※ 60일 컬럼은 TradingView 3개월(약 63거래일) 고저가 기준. 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)가 도달.</t>
         </is>
@@ -709,19 +791,19 @@
       <c r="C2" t="n">
         <v>7674.37</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="4" t="n">
         <v>0.43</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="5" t="n">
         <v>-1.43</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="4" t="n">
         <v>3.59</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="4" t="n">
         <v>3.07</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="4" t="n">
         <v>12.11</v>
       </c>
       <c r="I2" t="n">
@@ -747,19 +829,19 @@
       <c r="C3" t="n">
         <v>26180.46</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="4" t="n">
         <v>0.43</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="5" t="n">
         <v>-2.05</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="4" t="n">
         <v>4.15</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="5" t="n">
         <v>-0.43</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="4" t="n">
         <v>12.64</v>
       </c>
       <c r="I3" t="n">
@@ -785,19 +867,19 @@
       <c r="C4" t="n">
         <v>6912.95</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="4" t="n">
         <v>0.88</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="4" t="n">
         <v>1.46</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="4" t="n">
         <v>1.7</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="5" t="n">
         <v>-4.11</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="4" t="n">
         <v>64.04000000000001</v>
       </c>
       <c r="I4" t="n">
@@ -823,19 +905,19 @@
       <c r="C5" t="n">
         <v>66016.36</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="5" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="5" t="n">
         <v>-3.93</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="5" t="n">
         <v>-0.15</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="4" t="n">
         <v>4.23</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="4" t="n">
         <v>31.14</v>
       </c>
       <c r="I5" t="n">
@@ -861,19 +943,19 @@
       <c r="C6" t="n">
         <v>3905.2</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="4" t="n">
         <v>0.04</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="5" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="4" t="n">
         <v>0.73</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="5" t="n">
         <v>-5.96</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="5" t="n">
         <v>-1.6</v>
       </c>
       <c r="I6" t="n">
@@ -899,19 +981,19 @@
       <c r="C7" t="n">
         <v>4618.9</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="4" t="n">
         <v>0.57</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="5" t="n">
         <v>-1.01</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="5" t="n">
         <v>-2.31</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="5" t="n">
         <v>-6.15</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="5" t="n">
         <v>-0.24</v>
       </c>
       <c r="I7" t="n">
@@ -937,19 +1019,19 @@
       <c r="C8" t="n">
         <v>26009.46</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="4" t="n">
         <v>1.21</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="4" t="n">
         <v>3.55</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="4" t="n">
         <v>3.17</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="4" t="n">
         <v>2.45</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="4" t="n">
         <v>1.48</v>
       </c>
       <c r="I8" t="n">
@@ -975,19 +1057,19 @@
       <c r="C9" t="n">
         <v>4766.16</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="4" t="n">
         <v>1.4</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="4" t="n">
         <v>1.24</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="4" t="n">
         <v>1.44</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" s="5" t="n">
         <v>-0.06</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" s="5" t="n">
         <v>-13.59</v>
       </c>
       <c r="I9" t="n">
@@ -1106,7 +1188,7 @@
       <c r="F2" t="n">
         <v>17</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1147,7 +1229,7 @@
       <c r="F3" t="n">
         <v>15</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1188,7 +1270,7 @@
       <c r="F4" t="n">
         <v>14</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1229,7 +1311,7 @@
       <c r="F5" t="n">
         <v>5</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1270,7 +1352,7 @@
       <c r="F6" t="n">
         <v>5</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1311,7 +1393,7 @@
       <c r="F7" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1352,7 +1434,7 @@
       <c r="F8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1393,7 +1475,7 @@
       <c r="F9" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1434,7 +1516,7 @@
       <c r="F10" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1475,7 +1557,7 @@
       <c r="F11" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1516,7 +1598,7 @@
       <c r="F12" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1557,7 +1639,7 @@
       <c r="F13" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1598,7 +1680,7 @@
       <c r="F14" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1639,7 +1721,7 @@
       <c r="F15" t="n">
         <v>-1</v>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1680,7 +1762,7 @@
       <c r="F16" t="n">
         <v>-7</v>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1721,7 +1803,7 @@
       <c r="F17" t="n">
         <v>-13</v>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1924,7 +2006,7 @@
       <c r="F22" t="n">
         <v>3</v>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1963,7 +2045,7 @@
       <c r="F23" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2002,7 +2084,7 @@
       <c r="F24" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2043,7 +2125,7 @@
       <c r="F25" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2082,7 +2164,7 @@
       <c r="F26" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2121,7 +2203,7 @@
       <c r="F27" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2162,7 +2244,7 @@
       <c r="F28" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2201,7 +2283,7 @@
       <c r="F29" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2242,7 +2324,7 @@
       <c r="F30" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2281,7 +2363,7 @@
       <c r="F31" t="n">
         <v>-1</v>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2320,7 +2402,7 @@
       <c r="F32" t="n">
         <v>-2</v>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2677,7 +2759,7 @@
       <c r="F41" t="n">
         <v>5</v>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2718,7 +2800,7 @@
       <c r="F42" t="n">
         <v>5</v>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2757,7 +2839,7 @@
       <c r="F43" t="n">
         <v>3</v>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2798,7 +2880,7 @@
       <c r="F44" t="n">
         <v>3</v>
       </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="G44" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2837,7 +2919,7 @@
       <c r="F45" t="n">
         <v>1</v>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="G45" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2876,7 +2958,7 @@
       <c r="F46" t="n">
         <v>1</v>
       </c>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="G46" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2917,7 +2999,7 @@
       <c r="F47" t="n">
         <v>1</v>
       </c>
-      <c r="G47" s="4" t="inlineStr">
+      <c r="G47" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2956,7 +3038,7 @@
       <c r="F48" t="n">
         <v>-1</v>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3393,7 +3475,7 @@
       <c r="F59" t="n">
         <v>4</v>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3434,7 +3516,7 @@
       <c r="F60" t="n">
         <v>2</v>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3475,7 +3557,7 @@
       <c r="F61" t="n">
         <v>1</v>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="G61" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3514,7 +3596,7 @@
       <c r="F62" t="n">
         <v>1</v>
       </c>
-      <c r="G62" s="4" t="inlineStr">
+      <c r="G62" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3553,7 +3635,7 @@
       <c r="F63" t="n">
         <v>-1</v>
       </c>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="G63" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3594,7 +3676,7 @@
       <c r="F64" t="n">
         <v>-1</v>
       </c>
-      <c r="G64" s="5" t="inlineStr">
+      <c r="G64" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3635,7 +3717,7 @@
       <c r="F65" t="n">
         <v>-2</v>
       </c>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="G65" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -4101,30 +4183,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U47"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="95" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="6" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4145,90 +4228,95 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>1D</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>1주</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>YTD26</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>순위26</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>YTD25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>순위25</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>YTD24</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>순위24</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>YTD23</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>순위23</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>YTD22</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>순위22</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>YTD21</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>순위21</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YTD20</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>순위20</t>
         </is>
@@ -4250,58 +4338,63 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>0.1퍼센트로 제자리. 소프트웨어는 신고가 18종인데 반도체·하드웨어 7종이 신저가로 갈렸다</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="F2" s="9" t="n">
         <v>-3.5</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="G2" s="9" t="n">
         <v>2.7</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="H2" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="I2" s="9" t="n">
         <v>27.6</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="K2" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="M2" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="6" t="n">
+      <c r="O2" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="Q2" s="9" t="n">
         <v>-27.7</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>9</v>
       </c>
-      <c r="R2" s="6" t="n">
+      <c r="S2" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>4</v>
       </c>
-      <c r="T2" s="6" t="n">
+      <c r="U2" s="9" t="n">
         <v>43.6</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4321,58 +4414,63 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>1.3퍼센트 상승. 주간 4.3퍼센트·3개월 18.4퍼센트로 방어주 순환매의 최대 수혜 업종</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="9" t="n">
         <v>4.3</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="9" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="H3" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="I3" s="9" t="n">
         <v>13.8</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>5</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="K3" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="n">
+      <c r="O3" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="Q3" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>4</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="S3" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="T3" s="6" t="n">
+      <c r="U3" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4392,58 +4490,63 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>0.9퍼센트 상승. 장기금리 상승이 이자마진에 우호적이라 신고가 5종, 주간으로는 소폭 마이너스</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="H4" s="9" t="n">
         <v>11.5</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="9" t="n">
         <v>5.9</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="O4" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>7</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="Q4" s="9" t="n">
         <v>-10.6</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="S4" s="9" t="n">
         <v>34.8</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="U4" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4463,58 +4566,63 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>1.1퍼센트 반등했으나 연초 대비 마이너스 0.8퍼센트로 11개 업종 중 10위, 소비 회복은 아직 미약</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G5" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H5" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="M5" s="9" t="n">
         <v>26.5</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="O5" s="9" t="n">
         <v>39.6</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="Q5" s="9" t="n">
         <v>-36.3</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>10</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="S5" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="U5" s="9" t="n">
         <v>29.6</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4534,58 +4642,63 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>0.7퍼센트 상승에도 연초 대비 마이너스 4.8퍼센트로 최하위, 3개월 흐름도 계속 뒤처진다</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="9" t="n">
         <v>5.7</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="H6" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="I6" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>11</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K6" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="M6" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="O6" s="9" t="n">
         <v>52.8</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="Q6" s="9" t="n">
         <v>-37.6</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>11</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="S6" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>11</v>
       </c>
-      <c r="T6" s="6" t="n">
+      <c r="U6" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4605,58 +4718,63 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>0.3퍼센트 소폭 상승. 주간 마이너스 3.4퍼센트로 최근 한 달 모멘텀이 눈에 띄게 식었다</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="F7" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="G7" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="H7" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="I7" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>4</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="O7" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="Q7" s="9" t="n">
         <v>-5.6</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>5</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="S7" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="T7" s="6" t="n">
+      <c r="U7" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4676,58 +4794,63 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>0.8퍼센트 상승. 금리 부담에도 유틸리티와 달리 버텨 연초 대비 12.1퍼센트를 지켰다</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="F8" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="H8" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="I8" s="9" t="n">
         <v>12.1</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>7</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="K8" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="M8" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="O8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>10</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="Q8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>3</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="S8" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>10</v>
       </c>
-      <c r="T8" s="6" t="n">
+      <c r="U8" s="9" t="n">
         <v>10.1</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4747,58 +4870,63 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>0.2퍼센트 하락했지만 연초 대비 44.3퍼센트로 11개 업종 1위, 유가 반등에 주간은 2.8퍼센트 플러스</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="F9" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="G9" s="9" t="n">
         <v>7.2</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="H9" s="9" t="n">
         <v>8.4</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="I9" s="9" t="n">
         <v>44.3</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="M9" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="O9" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>9</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="Q9" s="9" t="n">
         <v>64.3</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="S9" s="9" t="n">
         <v>53.3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="6" t="n">
+      <c r="U9" s="9" t="n">
         <v>-32.7</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4818,58 +4946,63 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>2.3퍼센트 급락으로 유일한 약세. 장기금리 고착에 한 달 마이너스 7.4퍼센트, 신저가 14종 배출</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
         <v>-2.3</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="F10" s="9" t="n">
         <v>-3.5</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="G10" s="9" t="n">
         <v>-7.4</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="H10" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="I10" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>9</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="K10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="M10" s="9" t="n">
         <v>23.3</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="O10" s="9" t="n">
         <v>-7.2</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>11</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="Q10" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="S10" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="T10" s="6" t="n">
+      <c r="U10" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4889,58 +5022,63 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>2.1퍼센트로 당일 1위. 금·구리 광산주가 신고가 15종을 쏟아내며 업종 전체를 끌어올렸다</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="F11" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="G11" s="9" t="n">
         <v>6.5</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="H11" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="I11" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="9" t="n">
         <v>9.9</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>7</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="O11" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="Q11" s="9" t="n">
         <v>-12.3</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="S11" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="U11" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4960,58 +5098,63 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>보합. 금리 민감도가 큰데도 유틸리티와 달리 버텼고 연초 대비 13.5퍼센트를 유지 중</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="F12" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="G12" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="H12" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="I12" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>6</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="K12" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="M12" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="O12" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>6</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="Q12" s="9" t="n">
         <v>-26.2</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>8</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="S12" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="U12" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5031,58 +5174,59 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="F13" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="G13" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="H13" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="I13" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>6</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="K13" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>15</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="M13" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="O13" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>13</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="Q13" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>10</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="S13" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>11</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="U13" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5102,58 +5246,59 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="8" t="inlineStr"/>
+      <c r="E14" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="F14" s="9" t="n">
         <v>3.7</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="9" t="n">
         <v>5.9</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="H14" s="9" t="n">
         <v>4.2</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="I14" s="9" t="n">
         <v>22.5</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>5</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="K14" s="9" t="n">
         <v>41.4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>6</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="9" t="n">
         <v>29.9</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="O14" s="9" t="n">
         <v>37.2</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="Q14" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="S14" s="9" t="n">
         <v>39.3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="U14" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>17</v>
       </c>
     </row>
@@ -5173,58 +5318,59 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="8" t="inlineStr"/>
+      <c r="E15" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="F15" s="9" t="n">
         <v>-3.5</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="G15" s="9" t="n">
         <v>-5.3</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="H15" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="I15" s="9" t="n">
         <v>5.2</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>14</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="K15" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="M15" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>6</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="O15" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>9</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="Q15" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>12</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="S15" s="9" t="n">
         <v>12.6</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>8</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="U15" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5244,58 +5390,59 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="8" t="inlineStr"/>
+      <c r="E16" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="F16" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="G16" s="9" t="n">
         <v>-2.7</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="H16" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="I16" s="9" t="n">
         <v>20.9</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>7</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="K16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>17</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="M16" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>16</v>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="O16" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>12</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="Q16" s="9" t="n">
         <v>-9.4</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>14</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="S16" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>14</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="U16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5315,58 +5462,59 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="8" t="inlineStr"/>
+      <c r="E17" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="F17" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="9" t="n">
         <v>4.9</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="H17" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="I17" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>13</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="K17" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>16</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="M17" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>13</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="O17" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>17</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="Q17" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="S17" s="9" t="n">
         <v>-8.4</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>17</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="U17" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5386,58 +5534,59 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="8" t="inlineStr"/>
+      <c r="E18" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="F18" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="G18" s="9" t="n">
         <v>6.5</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="H18" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="I18" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>16</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="K18" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>14</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="M18" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>11</v>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="O18" s="9" t="n">
         <v>40.5</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="Q18" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>16</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="S18" s="9" t="n">
         <v>27.8</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="T18" s="6" t="n">
+      <c r="U18" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5457,58 +5606,59 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="F19" s="9" t="n">
         <v>-3.7</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="G19" s="9" t="n">
         <v>5.2</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="H19" s="9" t="n">
         <v>-7.8</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="I19" s="9" t="n">
         <v>47.3</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="K19" s="9" t="n">
         <v>68.8</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="M19" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="O19" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>4</v>
       </c>
-      <c r="P19" s="6" t="n">
+      <c r="Q19" s="9" t="n">
         <v>16.1</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>5</v>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="S19" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="U19" s="9" t="n">
         <v>-8.6</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5528,58 +5678,59 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="8" t="inlineStr"/>
+      <c r="E20" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="F20" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="G20" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="H20" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="I20" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>9</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="K20" s="9" t="n">
         <v>31.1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="M20" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="O20" s="9" t="n">
         <v>33.9</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>6</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="Q20" s="9" t="n">
         <v>-9.9</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>15</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="S20" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>9</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="U20" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5599,58 +5750,59 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="8" t="inlineStr"/>
+      <c r="E21" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="F21" s="9" t="n">
         <v>-7.2</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="G21" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="H21" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="I21" s="9" t="n">
         <v>31.4</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>3</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="K21" s="9" t="n">
         <v>27.5</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="M21" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>10</v>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="O21" s="9" t="n">
         <v>33.7</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>7</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="Q21" s="9" t="n">
         <v>-23</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>17</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="S21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>5</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="U21" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5670,58 +5822,59 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="8" t="inlineStr"/>
+      <c r="E22" s="9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="F22" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="G22" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="H22" s="9" t="n">
         <v>10.4</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="I22" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>10</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="K22" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>13</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="M22" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="O22" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>15</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="Q22" s="9" t="n">
         <v>-5.9</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>13</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="S22" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>13</v>
       </c>
-      <c r="T22" s="6" t="n">
+      <c r="U22" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5741,58 +5894,59 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="8" t="inlineStr"/>
+      <c r="E23" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="F23" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="G23" s="9" t="n">
         <v>5.3</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="H23" s="9" t="n">
         <v>5.4</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="I23" s="9" t="n">
         <v>7.2</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>12</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="K23" s="9" t="n">
         <v>37.4</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>7</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="M23" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>15</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="O23" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="Q23" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>7</v>
       </c>
-      <c r="R23" s="6" t="n">
+      <c r="S23" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>16</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="U23" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5812,58 +5966,59 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="8" t="inlineStr"/>
+      <c r="E24" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="F24" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="G24" s="9" t="n">
         <v>4.8</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="H24" s="9" t="n">
         <v>10.1</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="I24" s="9" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>11</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="K24" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>11</v>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="M24" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>17</v>
       </c>
-      <c r="N24" s="6" t="n">
+      <c r="O24" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>14</v>
       </c>
-      <c r="P24" s="6" t="n">
+      <c r="Q24" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>8</v>
       </c>
-      <c r="R24" s="6" t="n">
+      <c r="S24" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>12</v>
       </c>
-      <c r="T24" s="6" t="n">
+      <c r="U24" s="9" t="n">
         <v>-17.1</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>16</v>
       </c>
     </row>
@@ -5883,58 +6038,59 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="F25" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="G25" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="H25" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="I25" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>8</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="K25" s="9" t="n">
         <v>41.5</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="M25" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>9</v>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="O25" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="Q25" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>3</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="S25" s="9" t="n">
         <v>29.2</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="T25" s="6" t="n">
+      <c r="U25" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5954,58 +6110,59 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="8" t="inlineStr"/>
+      <c r="E26" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="F26" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="G26" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="H26" s="9" t="n">
         <v>6.1</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="I26" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>15</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="K26" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>12</v>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="M26" s="9" t="n">
         <v>23.4</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="O26" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>16</v>
       </c>
-      <c r="P26" s="6" t="n">
+      <c r="Q26" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>9</v>
       </c>
-      <c r="R26" s="6" t="n">
+      <c r="S26" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>15</v>
       </c>
-      <c r="T26" s="6" t="n">
+      <c r="U26" s="9" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6025,58 +6182,59 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="F27" s="9" t="n">
         <v>-4.5</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="G27" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="H27" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="I27" s="9" t="n">
         <v>43.8</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="K27" s="9" t="n">
         <v>44.8</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="6" t="n">
+      <c r="M27" s="9" t="n">
         <v>50.4</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="O27" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" s="6" t="n">
+      <c r="Q27" s="9" t="n">
         <v>38.3</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" s="6" t="n">
+      <c r="S27" s="9" t="n">
         <v>26.7</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>4</v>
       </c>
-      <c r="T27" s="6" t="n">
+      <c r="U27" s="9" t="n">
         <v>-16.3</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>15</v>
       </c>
     </row>
@@ -6096,58 +6254,59 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="8" t="inlineStr"/>
+      <c r="E28" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="F28" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="G28" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="H28" s="9" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="I28" s="9" t="n">
         <v>26.5</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>4</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="K28" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>10</v>
       </c>
-      <c r="L28" s="6" t="n">
+      <c r="M28" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="O28" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>10</v>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="Q28" s="9" t="n">
         <v>13.7</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>6</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="S28" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>6</v>
       </c>
-      <c r="T28" s="6" t="n">
+      <c r="U28" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6167,58 +6326,59 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="8" t="inlineStr"/>
+      <c r="E29" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="F29" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="G29" s="9" t="n">
         <v>-5.2</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="H29" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="I29" s="9" t="n">
         <v>-5.4</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>17</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="K29" s="9" t="n">
         <v>41.6</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>4</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="M29" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>12</v>
       </c>
-      <c r="N29" s="6" t="n">
+      <c r="O29" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>11</v>
       </c>
-      <c r="P29" s="6" t="n">
+      <c r="Q29" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>11</v>
       </c>
-      <c r="R29" s="6" t="n">
+      <c r="S29" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>10</v>
       </c>
-      <c r="T29" s="6" t="n">
+      <c r="U29" s="9" t="n">
         <v>-13.3</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>14</v>
       </c>
     </row>
@@ -6238,58 +6398,63 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>1.1퍼센트 상승, 주간 3.5퍼센트로 4개 시장 중 가장 강했다. 광산주가 지수를 끌었다</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="F30" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="G30" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="H30" s="9" t="n">
         <v>3.4</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="I30" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="K30" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="M30" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>3</v>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="O30" s="9" t="n">
         <v>-13.7</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" s="6" t="n">
+      <c r="Q30" s="9" t="n">
         <v>-15.3</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" s="6" t="n">
+      <c r="S30" s="9" t="n">
         <v>-14.2</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" s="6" t="n">
+      <c r="U30" s="9" t="n">
         <v>-3.7</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6309,58 +6474,63 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>0.8퍼센트 상승, 주간 3.9퍼센트로 본토 A주보다 강해 홍콩 선호가 이어졌다</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="F31" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="G31" s="9" t="n">
         <v>3.6</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="H31" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="I31" s="9" t="n">
         <v>-2.5</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="K31" s="9" t="n">
         <v>22.9</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>2</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="M31" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="O31" s="9" t="n">
         <v>-14.1</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>3</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="Q31" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="R31" s="6" t="n">
+      <c r="S31" s="9" t="n">
         <v>-23.2</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>2</v>
       </c>
-      <c r="T31" s="6" t="n">
+      <c r="U31" s="9" t="n">
         <v>-4.1</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6380,56 +6550,61 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>1.4퍼센트 상승했으나 연초 대비 마이너스 13.4퍼센트로 기술주 회복은 아직 더디다</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="F32" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="G32" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="H32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="I32" s="9" t="n">
         <v>-13.4</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="K32" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="6" t="n">
+      <c r="M32" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>2</v>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="O32" s="9" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" s="6" t="n">
+      <c r="Q32" s="9" t="n">
         <v>-27.4</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>3</v>
       </c>
-      <c r="R32" s="6" t="n">
+      <c r="S32" s="9" t="n">
         <v>-32.9</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>3</v>
       </c>
-      <c r="T32" s="6" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" s="9" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6447,58 +6622,63 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>0.3퍼센트 보합권. 연초 대비 42.3퍼센트로 1위지만 한 달 마이너스 5.8퍼센트로 열기가 식는 중</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="F33" s="9" t="n">
         <v>-3.2</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="G33" s="9" t="n">
         <v>-5.8</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="H33" s="9" t="n">
         <v>-11.2</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="I33" s="9" t="n">
         <v>42.3</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="K33" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>5</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="M33" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>3</v>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="O33" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>4</v>
       </c>
-      <c r="P33" s="6" t="n">
+      <c r="Q33" s="9" t="n">
         <v>-36.6</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>12</v>
       </c>
-      <c r="R33" s="6" t="n">
+      <c r="S33" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>4</v>
       </c>
-      <c r="T33" s="6" t="n">
+      <c r="U33" s="9" t="n">
         <v>46.6</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6518,58 +6698,63 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>1.1퍼센트 상승. 연초 대비 28.4퍼센트는 지켰지만 최근 한 달은 마이너스로 돌아섰다</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="F34" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="G34" s="9" t="n">
         <v>-4.1</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="H34" s="9" t="n">
         <v>-9.1</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="I34" s="9" t="n">
         <v>28.4</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>3</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="K34" s="9" t="n">
         <v>52.1</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>4</v>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="M34" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>5</v>
       </c>
-      <c r="N34" s="6" t="n">
+      <c r="O34" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>3</v>
       </c>
-      <c r="P34" s="6" t="n">
+      <c r="Q34" s="9" t="n">
         <v>-34</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>11</v>
       </c>
-      <c r="R34" s="6" t="n">
+      <c r="S34" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>8</v>
       </c>
-      <c r="T34" s="6" t="n">
+      <c r="U34" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6589,58 +6774,63 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>2.6퍼센트 상승, 연초 대비 38.3퍼센트로 2위. 다만 3개월은 마이너스 12.9퍼센트로 조정 국면</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="F35" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="G35" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="H35" s="9" t="n">
         <v>-12.9</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="I35" s="9" t="n">
         <v>38.3</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="K35" s="9" t="n">
         <v>99.7</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>2</v>
       </c>
-      <c r="L35" s="6" t="n">
+      <c r="M35" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>4</v>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="O35" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>1</v>
       </c>
-      <c r="P35" s="6" t="n">
+      <c r="Q35" s="9" t="n">
         <v>-37.8</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>13</v>
       </c>
-      <c r="R35" s="6" t="n">
+      <c r="S35" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>6</v>
       </c>
-      <c r="T35" s="6" t="n">
+      <c r="U35" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6660,56 +6850,61 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>1.5퍼센트 반등했으나 3개월 마이너스 18.5퍼센트, 전기차 과잉경쟁 부담이 여전하다</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="F36" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="G36" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="H36" s="9" t="n">
         <v>-18.5</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="I36" s="9" t="n">
         <v>-12.1</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>8</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="K36" s="9" t="n">
         <v>56.6</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="M36" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>8</v>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="O36" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>12</v>
       </c>
-      <c r="P36" s="6" t="n">
+      <c r="Q36" s="9" t="n">
         <v>-28.9</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>10</v>
       </c>
-      <c r="R36" s="6" t="n">
+      <c r="S36" s="9" t="n">
         <v>41.9</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>2</v>
       </c>
-      <c r="T36" s="6" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" s="9" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6727,58 +6922,63 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>0.9퍼센트 반등. 3개월 마이너스 19.5퍼센트로 낙폭이 커 기술적 되돌림 성격으로 보인다</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="F37" s="9" t="n">
         <v>-3.9</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="G37" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="H37" s="9" t="n">
         <v>-19.5</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="I37" s="9" t="n">
         <v>-19.4</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>11</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="K37" s="9" t="n">
         <v>31.8</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>6</v>
       </c>
-      <c r="L37" s="6" t="n">
+      <c r="M37" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>6</v>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="O37" s="9" t="n">
         <v>-10.8</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>6</v>
       </c>
-      <c r="P37" s="6" t="n">
+      <c r="Q37" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>8</v>
       </c>
-      <c r="R37" s="6" t="n">
+      <c r="S37" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>5</v>
       </c>
-      <c r="T37" s="6" t="n">
+      <c r="U37" s="9" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6798,56 +6998,61 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>0.4퍼센트 소폭 상승. 3개월 마이너스 24.1퍼센트로 13개 업종 중 낙폭이 가장 깊다</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="F38" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="G38" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="H38" s="9" t="n">
         <v>-24.1</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="I38" s="9" t="n">
         <v>-11.4</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>7</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="K38" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>7</v>
       </c>
-      <c r="L38" s="6" t="n">
+      <c r="M38" s="9" t="n">
         <v>-14.9</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>13</v>
       </c>
-      <c r="N38" s="6" t="n">
+      <c r="O38" s="9" t="n">
         <v>-35.2</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>13</v>
       </c>
-      <c r="P38" s="6" t="n">
+      <c r="Q38" s="9" t="n">
         <v>-19.7</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>5</v>
       </c>
-      <c r="R38" s="6" t="n">
+      <c r="S38" s="9" t="n">
         <v>50.7</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" s="6" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" s="9" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6865,58 +7070,63 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>1.6퍼센트 하락, 연초 대비 마이너스 21.8퍼센트로 최하위. 주류 소비 위축이 가장 심각한 업종</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="F39" s="9" t="n">
         <v>-5</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="G39" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="H39" s="9" t="n">
         <v>-6.5</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="I39" s="9" t="n">
         <v>-21.8</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>13</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="K39" s="9" t="n">
         <v>-13</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>13</v>
       </c>
-      <c r="L39" s="6" t="n">
+      <c r="M39" s="9" t="n">
         <v>-11</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>11</v>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="O39" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>10</v>
       </c>
-      <c r="P39" s="6" t="n">
+      <c r="Q39" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>3</v>
       </c>
-      <c r="R39" s="6" t="n">
+      <c r="S39" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>9</v>
       </c>
-      <c r="T39" s="6" t="n">
+      <c r="U39" s="9" t="n">
         <v>336.4</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6936,58 +7146,63 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>0.4퍼센트 하락했지만 주간 2.3퍼센트·3개월 6.3퍼센트로 방어적 순환매는 유지된다</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="F40" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="G40" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="H40" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="I40" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>6</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="K40" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="6" t="n">
+      <c r="M40" s="9" t="n">
         <v>42.6</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="O40" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>5</v>
       </c>
-      <c r="P40" s="6" t="n">
+      <c r="Q40" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="R40" s="6" t="n">
+      <c r="S40" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>7</v>
       </c>
-      <c r="T40" s="6" t="n">
+      <c r="U40" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>10</v>
       </c>
     </row>
@@ -7007,58 +7222,63 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>3.3퍼센트로 A주 1위. 금값 4,600달러선 회복에 홍콩 금광주와 같은 재료를 공유했다</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="F41" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="G41" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="H41" s="9" t="n">
         <v>-3.9</v>
       </c>
-      <c r="H41" s="6" t="n">
+      <c r="I41" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>5</v>
       </c>
-      <c r="J41" s="6" t="n">
+      <c r="K41" s="9" t="n">
         <v>101.1</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" s="6" t="n">
+      <c r="M41" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>7</v>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="O41" s="9" t="n">
         <v>-11.4</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>7</v>
       </c>
-      <c r="P41" s="6" t="n">
+      <c r="Q41" s="9" t="n">
         <v>-21.6</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>6</v>
       </c>
-      <c r="R41" s="6" t="n">
+      <c r="S41" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>3</v>
       </c>
-      <c r="T41" s="6" t="n">
+      <c r="U41" s="9" t="n">
         <v>43.2</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7078,58 +7298,63 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>0.9퍼센트 하락. 3개월 마이너스 12.6퍼센트로 부동산 업황 회복 신호가 여전히 없다</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="F42" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="G42" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="H42" s="9" t="n">
         <v>-12.6</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="I42" s="9" t="n">
         <v>-19.4</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>11</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="K42" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>11</v>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="M42" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>9</v>
       </c>
-      <c r="N42" s="6" t="n">
+      <c r="O42" s="9" t="n">
         <v>-27</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>11</v>
       </c>
-      <c r="P42" s="6" t="n">
+      <c r="Q42" s="9" t="n">
         <v>-10.4</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>2</v>
       </c>
-      <c r="R42" s="6" t="n">
+      <c r="S42" s="9" t="n">
         <v>-6.4</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>11</v>
       </c>
-      <c r="T42" s="6" t="n">
+      <c r="U42" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>11</v>
       </c>
     </row>
@@ -7149,58 +7374,63 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>보합. 궈신증권이 신저가로 밀리는 등 거래대금 둔화 우려가 업종을 누르고 있다</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="F43" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="G43" s="9" t="n">
         <v>-5.8</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="H43" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="I43" s="9" t="n">
         <v>-12.2</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>9</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="K43" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>10</v>
       </c>
-      <c r="L43" s="6" t="n">
+      <c r="M43" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>2</v>
       </c>
-      <c r="N43" s="6" t="n">
+      <c r="O43" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>2</v>
       </c>
-      <c r="P43" s="6" t="n">
+      <c r="Q43" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>8</v>
       </c>
-      <c r="R43" s="6" t="n">
+      <c r="S43" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>10</v>
       </c>
-      <c r="T43" s="6" t="n">
+      <c r="U43" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7220,58 +7450,63 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>3.0퍼센트 급락으로 당일 최하위. 다만 3개월 14.1퍼센트로 A주에서 가장 강했던 업종의 차익실현</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="F44" s="9" t="n">
         <v>-1.8</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="G44" s="9" t="n">
         <v>2.9</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="H44" s="9" t="n">
         <v>14.1</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="I44" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>4</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="K44" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>9</v>
       </c>
-      <c r="L44" s="6" t="n">
+      <c r="M44" s="9" t="n">
         <v>-12.2</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>12</v>
       </c>
-      <c r="N44" s="6" t="n">
+      <c r="O44" s="9" t="n">
         <v>-14</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>8</v>
       </c>
-      <c r="P44" s="6" t="n">
+      <c r="Q44" s="9" t="n">
         <v>-24.5</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>7</v>
       </c>
-      <c r="R44" s="6" t="n">
+      <c r="S44" s="9" t="n">
         <v>-15.7</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>13</v>
       </c>
-      <c r="T44" s="6" t="n">
+      <c r="U44" s="9" t="n">
         <v>62.9</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7291,58 +7526,63 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>1.5퍼센트 하락. 연초 대비 마이너스 16.9퍼센트로 내수 소비 부진이 계속 확인된다</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="F45" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="G45" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="H45" s="9" t="n">
         <v>-3.2</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="I45" s="9" t="n">
         <v>-16.9</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>10</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="K45" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>12</v>
       </c>
-      <c r="L45" s="6" t="n">
+      <c r="M45" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>10</v>
       </c>
-      <c r="N45" s="6" t="n">
+      <c r="O45" s="9" t="n">
         <v>-18.3</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>9</v>
       </c>
-      <c r="P45" s="6" t="n">
+      <c r="Q45" s="9" t="n">
         <v>-13.4</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>4</v>
       </c>
-      <c r="R45" s="6" t="n">
+      <c r="S45" s="9" t="n">
         <v>-7.5</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>12</v>
       </c>
-      <c r="T45" s="6" t="n">
+      <c r="U45" s="9" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7354,7 +7594,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D45">
+  <conditionalFormatting sqref="E2:E45">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-3"/>
@@ -7366,7 +7606,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E45">
+  <conditionalFormatting sqref="F2:F45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="-7.2"/>
@@ -7378,7 +7618,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F45">
+  <conditionalFormatting sqref="G2:G45">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="-7.4"/>
@@ -7390,7 +7630,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G45">
+  <conditionalFormatting sqref="H2:H45">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="-24.1"/>
@@ -7402,7 +7642,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H45">
+  <conditionalFormatting sqref="I2:I45">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="-21.8"/>
@@ -7414,7 +7654,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J45">
+  <conditionalFormatting sqref="K2:K45">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="-13"/>
@@ -7426,7 +7666,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L45">
+  <conditionalFormatting sqref="M2:M45">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="-14.9"/>
@@ -7438,7 +7678,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N45">
+  <conditionalFormatting sqref="O2:O45">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="-35.2"/>
@@ -7450,7 +7690,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P45">
+  <conditionalFormatting sqref="Q2:Q45">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="-37.8"/>
@@ -7462,7 +7702,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R45">
+  <conditionalFormatting sqref="S2:S45">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="-32.9"/>
@@ -7474,7 +7714,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T45">
+  <conditionalFormatting sqref="U2:U45">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-32.7"/>
@@ -7588,7 +7828,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7635,19 +7875,19 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="N2" s="10" t="inlineStr">
         <is>
           <t>(전일) (대형마트 소매유통) 실적 상회·연간 상향에도 미국 동일점포 2.6%와 3분기 이익 가이던스 부진</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7691,15 +7931,15 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="7" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7747,15 +7987,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7799,15 +8039,15 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="7" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7851,15 +8091,15 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="7" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7903,15 +8143,15 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7959,15 +8199,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N8" s="7" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8011,15 +8251,19 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="7" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>(페루·멕시코 구리광산) 구리 강세 랠리와 2분기 실적 서프라이즈에 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8061,15 +8305,15 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="7" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8113,10 +8357,10 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="7" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8169,14 +8413,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N12" s="7" t="inlineStr">
+      <c r="N12" s="10" t="inlineStr">
         <is>
           <t>(전일) (셰일 원유·가스 개발) 유가 강세와 2분기 실적 호조로 52주 신고가</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8225,15 +8469,15 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="7" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8281,10 +8525,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N14" s="7" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8333,10 +8577,10 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="7" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8385,10 +8629,10 @@
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" s="7" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8437,19 +8681,19 @@
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" s="7" t="inlineStr">
+      <c r="N17" s="10" t="inlineStr">
         <is>
           <t>(전일) 아그니코이글마인스(금 채굴): 달러 약세와 장기금리 반락으로 금값 급등 수혜</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8497,15 +8741,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N18" s="7" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr">
+        <is>
+          <t>(글로벌 구리광산 대형주) 구리 재고 타이트·AI 전력수요 기대에 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8549,10 +8797,10 @@
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" s="7" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8605,15 +8853,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N20" s="7" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8661,15 +8909,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N21" s="7" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8713,10 +8961,14 @@
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" s="7" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr">
+        <is>
+          <t>(전력 규제 유틸리티) 금리 상승기 고배당 유틸리티 동반 하락</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8765,15 +9017,15 @@
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" s="7" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8817,10 +9069,10 @@
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" s="7" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8869,10 +9121,10 @@
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" s="7" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8921,15 +9173,15 @@
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" s="7" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8973,15 +9225,15 @@
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" s="7" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9023,10 +9275,10 @@
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" s="7" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9075,15 +9327,15 @@
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" s="7" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9131,10 +9383,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N30" s="7" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9187,10 +9439,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N31" s="7" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9239,15 +9491,15 @@
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" s="7" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9295,10 +9547,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N33" s="7" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9347,15 +9599,15 @@
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" s="7" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9399,10 +9651,14 @@
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" s="7" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr">
+        <is>
+          <t>(전력 규제 유틸리티) 국채금리 상승 압력에 유틸리티 섹터 전반 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9455,10 +9711,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N36" s="7" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9507,10 +9763,10 @@
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" s="7" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9559,15 +9815,15 @@
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" s="7" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9611,10 +9867,14 @@
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" s="7" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr">
+        <is>
+          <t>(전력·가스 규제 유틸리티) 장기 국채금리 고공행진에 금리민감주 동반 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9667,14 +9927,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N40" s="7" t="inlineStr">
+      <c r="N40" s="10" t="inlineStr">
         <is>
           <t>(전일) 벡톤디킨슨(주사기·진단 등 의료기기): 개별 뉴스 없음, 헬스케어 랠리 동반 상승</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9723,15 +9983,15 @@
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" s="7" t="inlineStr"/>
+      <c r="N41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9775,15 +10035,15 @@
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" s="7" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9827,10 +10087,14 @@
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" s="7" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr">
+        <is>
+          <t>(전력 규제 유틸리티) 장기금리 상승으로 배당주 매력 훼손, 매도 압력</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9883,10 +10147,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N44" s="7" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr">
+        <is>
+          <t>(생명과학 분석장비) 뚜렷한 촉매 없이 실적 앞둔 매수세로 52주 고가 돌파</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9939,10 +10207,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N45" s="7" t="inlineStr"/>
+      <c r="N45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9991,10 +10259,10 @@
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" s="7" t="inlineStr"/>
+      <c r="N46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10043,19 +10311,19 @@
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" s="7" t="inlineStr">
+      <c r="N47" s="10" t="inlineStr">
         <is>
           <t>(전일) (금 채굴) 금값 2개월래 최고 4530달러 부근, 금광주 동반 신고가</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10099,10 +10367,14 @@
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" s="7" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr">
+        <is>
+          <t>(프레스티지 화장품) 분기 EPS 서프라이즈와 중국 매출 회복에 목표가 줄상향</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10151,15 +10423,15 @@
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" s="7" t="inlineStr"/>
+      <c r="N49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10207,10 +10479,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N50" s="7" t="inlineStr"/>
+      <c r="N50" s="10" t="inlineStr">
+        <is>
+          <t>(전력·가스 규제 유틸리티) 국채수익률 고점권 유지에 금리민감주 매도</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10259,15 +10535,15 @@
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" s="7" t="inlineStr"/>
+      <c r="N51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10315,15 +10591,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N52" s="7" t="inlineStr"/>
+      <c r="N52" s="10" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10367,10 +10643,10 @@
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" s="7" t="inlineStr"/>
+      <c r="N53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10419,10 +10695,10 @@
         </is>
       </c>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" s="7" t="inlineStr"/>
+      <c r="N54" s="10" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10475,14 +10751,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N55" s="7" t="inlineStr">
+      <c r="N55" s="10" t="inlineStr">
         <is>
           <t>(전일) (유전체 시퀀싱 장비) 2분기 매출 서프라이즈 여진에 신고가 지속</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10531,15 +10807,15 @@
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" s="7" t="inlineStr"/>
+      <c r="N56" s="10" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10583,10 +10859,10 @@
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" s="7" t="inlineStr"/>
+      <c r="N57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10635,15 +10911,15 @@
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" s="7" t="inlineStr"/>
+      <c r="N58" s="10" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10687,10 +10963,10 @@
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" s="7" t="inlineStr"/>
+      <c r="N59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10739,15 +11015,15 @@
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" s="7" t="inlineStr"/>
+      <c r="N60" s="10" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+      <c r="A61" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10791,10 +11067,10 @@
         </is>
       </c>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" s="7" t="inlineStr"/>
+      <c r="N61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10843,10 +11119,10 @@
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" s="7" t="inlineStr"/>
+      <c r="N62" s="10" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10895,14 +11171,14 @@
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" s="7" t="inlineStr">
+      <c r="N63" s="10" t="inlineStr">
         <is>
           <t>(전일) 커티스라이트(방산·원자력 부품): 특별한 뉴스 없음(8월 실적 이후 밸류에이션 조정 지속)</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10951,15 +11227,15 @@
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" s="7" t="inlineStr"/>
+      <c r="N64" s="10" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11007,10 +11283,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N65" s="7" t="inlineStr"/>
+      <c r="N65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11057,10 +11333,10 @@
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" s="7" t="inlineStr"/>
+      <c r="N66" s="10" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11109,10 +11385,10 @@
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" s="7" t="inlineStr"/>
+      <c r="N67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11161,19 +11437,19 @@
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
-      <c r="N68" s="7" t="inlineStr">
+      <c r="N68" s="10" t="inlineStr">
         <is>
           <t>(전일) 코어마이닝(금·은 채굴): 금 4.8%·은 4.8% 급등에 신고가 경신</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="inlineStr">
+      <c r="A69" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11221,15 +11497,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N69" s="7" t="inlineStr"/>
+      <c r="N69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11273,10 +11549,10 @@
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" s="7" t="inlineStr"/>
+      <c r="N70" s="10" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11325,15 +11601,15 @@
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" s="7" t="inlineStr"/>
+      <c r="N71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11377,15 +11653,15 @@
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" s="7" t="inlineStr"/>
+      <c r="N72" s="10" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11429,15 +11705,15 @@
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" s="7" t="inlineStr"/>
+      <c r="N73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="inlineStr">
+      <c r="A74" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11481,15 +11757,15 @@
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" s="7" t="inlineStr"/>
+      <c r="N74" s="10" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11537,10 +11813,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N75" s="7" t="inlineStr"/>
+      <c r="N75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11593,14 +11869,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N76" s="7" t="inlineStr">
+      <c r="N76" s="10" t="inlineStr">
         <is>
           <t>(전일) (산업용 접착·도포장비) 3분기 EPS 3.25달러로 컨센 상회, 가이던스 상향</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11653,15 +11929,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N77" s="7" t="inlineStr"/>
+      <c r="N77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11709,15 +11985,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N78" s="7" t="inlineStr"/>
+      <c r="N78" s="10" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11761,15 +12037,15 @@
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" s="7" t="inlineStr"/>
+      <c r="N79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="A80" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11813,10 +12089,10 @@
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" s="7" t="inlineStr"/>
+      <c r="N80" s="10" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="inlineStr">
+      <c r="A81" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11865,10 +12141,10 @@
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
-      <c r="N81" s="7" t="inlineStr"/>
+      <c r="N81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="inlineStr">
+      <c r="A82" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11917,15 +12193,15 @@
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
-      <c r="N82" s="7" t="inlineStr"/>
+      <c r="N82" s="10" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="inlineStr">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11969,10 +12245,10 @@
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
-      <c r="N83" s="7" t="inlineStr"/>
+      <c r="N83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="inlineStr">
+      <c r="A84" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12021,10 +12297,10 @@
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
-      <c r="N84" s="7" t="inlineStr"/>
+      <c r="N84" s="10" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="inlineStr">
+      <c r="A85" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12073,10 +12349,10 @@
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
-      <c r="N85" s="7" t="inlineStr"/>
+      <c r="N85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="inlineStr">
+      <c r="A86" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12129,10 +12405,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N86" s="7" t="inlineStr"/>
+      <c r="N86" s="10" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="inlineStr">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12185,10 +12461,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N87" s="7" t="inlineStr"/>
+      <c r="N87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12237,19 +12513,19 @@
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
-      <c r="N88" s="7" t="inlineStr">
+      <c r="N88" s="10" t="inlineStr">
         <is>
           <t>(전일) 헤클라마이닝(은 채굴): 금리인상 우려 후퇴로 금·은값 급등, 광산주 동반 강세</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="inlineStr">
+      <c r="A89" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12293,10 +12569,14 @@
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
-      <c r="N89" s="7" t="inlineStr"/>
+      <c r="N89" s="10" t="inlineStr">
+        <is>
+          <t>(저가 잡화 소매체인) 실적 발표를 앞둔 매수세와 목표가 상향</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="inlineStr">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12343,15 +12623,15 @@
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
-      <c r="N90" s="7" t="inlineStr"/>
+      <c r="N90" s="10" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="inlineStr">
+      <c r="A91" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12399,10 +12679,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N91" s="7" t="inlineStr"/>
+      <c r="N91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="inlineStr">
+      <c r="A92" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12451,14 +12731,14 @@
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
-      <c r="N92" s="7" t="inlineStr">
+      <c r="N92" s="10" t="inlineStr">
         <is>
           <t>(전일) (태양광 트래커·에너지저장) 실적 부진과 목표주가 하향 여진 추정</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="inlineStr">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12503,14 +12783,14 @@
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
-      <c r="N93" s="7" t="inlineStr">
-        <is>
-          <t>(전일) (AI 정밀의료 데이터분석) 특별한 뉴스 없음, AI헬스케어 순환매 유입 추정</t>
+      <c r="N93" s="10" t="inlineStr">
+        <is>
+          <t>(AI 정밀의료 유전체분석) 흑색종 임상 성공 후광과 자체 가이던스 상향 랠리</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="4" t="inlineStr">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12563,10 +12843,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N94" s="7" t="inlineStr"/>
+      <c r="N94" s="10" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="inlineStr">
+      <c r="A95" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12617,14 +12897,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N95" s="7" t="inlineStr">
+      <c r="N95" s="10" t="inlineStr">
         <is>
           <t>(전일) (산업용 송풍·공조장비) 51억유로 규모 인수 자금조달 부담 우려로 신저가</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="inlineStr">
+      <c r="A96" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12673,10 +12953,10 @@
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
-      <c r="N96" s="7" t="inlineStr"/>
+      <c r="N96" s="10" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="inlineStr">
+      <c r="A97" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12729,19 +13009,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N97" s="7" t="inlineStr">
+      <c r="N97" s="10" t="inlineStr">
         <is>
           <t>(전일) 왓츠코(냉난방공조 유통): 30년물 금리 2007년래 최고에 주택·건자재 수요 우려 확산</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="4" t="inlineStr">
+      <c r="A98" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B98" s="8" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12785,10 +13065,10 @@
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
-      <c r="N98" s="7" t="inlineStr"/>
+      <c r="N98" s="10" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="inlineStr">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12835,15 +13115,15 @@
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
-      <c r="N99" s="7" t="inlineStr"/>
+      <c r="N99" s="10" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="4" t="inlineStr">
+      <c r="A100" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B100" s="8" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12891,10 +13171,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N100" s="7" t="inlineStr"/>
+      <c r="N100" s="10" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="4" t="inlineStr">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12943,10 +13223,10 @@
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
-      <c r="N101" s="7" t="inlineStr"/>
+      <c r="N101" s="10" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="4" t="inlineStr">
+      <c r="A102" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12995,15 +13275,19 @@
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
-      <c r="N102" s="7" t="inlineStr"/>
+      <c r="N102" s="10" t="inlineStr">
+        <is>
+          <t>(캐나다계 금광 채굴) 금값 3개월래 최고치 랠리와 CIBC 투자의견 상향</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" s="5" t="inlineStr">
+      <c r="A103" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B103" s="8" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13047,10 +13331,10 @@
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
-      <c r="N103" s="7" t="inlineStr"/>
+      <c r="N103" s="10" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="4" t="inlineStr">
+      <c r="A104" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13099,10 +13383,10 @@
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
-      <c r="N104" s="7" t="inlineStr"/>
+      <c r="N104" s="10" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="5" t="inlineStr">
+      <c r="A105" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13149,19 +13433,19 @@
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
-      <c r="N105" s="7" t="inlineStr">
+      <c r="N105" s="10" t="inlineStr">
         <is>
           <t>(전일) 인라이트리뉴어블(태양광·풍력 발전 개발): 특별한 뉴스 없음(밸류에이션 부담·차익실현 추정)</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="4" t="inlineStr">
+      <c r="A106" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B106" s="8" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13205,10 +13489,10 @@
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
-      <c r="N106" s="7" t="inlineStr"/>
+      <c r="N106" s="10" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="inlineStr">
+      <c r="A107" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13255,10 +13539,10 @@
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
-      <c r="N107" s="7" t="inlineStr"/>
+      <c r="N107" s="10" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="inlineStr">
+      <c r="A108" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13307,10 +13591,10 @@
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
-      <c r="N108" s="7" t="inlineStr"/>
+      <c r="N108" s="10" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="inlineStr">
+      <c r="A109" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13359,15 +13643,15 @@
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
-      <c r="N109" s="7" t="inlineStr"/>
+      <c r="N109" s="10" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="inlineStr">
+      <c r="A110" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B110" s="8" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13411,15 +13695,15 @@
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
-      <c r="N110" s="7" t="inlineStr"/>
+      <c r="N110" s="10" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="inlineStr">
+      <c r="A111" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B111" s="8" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13467,10 +13751,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N111" s="7" t="inlineStr"/>
+      <c r="N111" s="10" t="inlineStr">
+        <is>
+          <t>(전자시장조성 트레이딩) 브로커리지 부문 35~40억달러 매각 검토설에 급등</t>
+        </is>
+      </c>
     </row>
     <row r="112">
-      <c r="A112" s="4" t="inlineStr">
+      <c r="A112" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13519,10 +13807,10 @@
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
-      <c r="N112" s="7" t="inlineStr"/>
+      <c r="N112" s="10" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="inlineStr">
+      <c r="A113" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13575,14 +13863,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N113" s="7" t="inlineStr">
+      <c r="N113" s="10" t="inlineStr">
         <is>
           <t>(전일) (생명과학 진단·시약) 2분기 EPS 2.62달러로 컨센 상회</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="4" t="inlineStr">
+      <c r="A114" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13631,7 +13919,7 @@
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
-      <c r="N114" s="7" t="inlineStr"/>
+      <c r="N114" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N114"/>
@@ -13737,12 +14025,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13784,15 +14072,19 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="7" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>(유니클로 운영 의류업체) 미국 대형 유통 실적 부진 여파로 소비주 동반 급락</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13838,10 +14130,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>(일본 통신 1위 NTT그룹) 방어주 선호 속 매수세로 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13892,19 +14188,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) (자동차 제조) 미 장기금리 급락에 할부금융 우려 완화, 7월 수출 호조</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13946,10 +14242,14 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="7" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>(공조기기 세계 1위) 8월 초 분기 실적 부진의 여진으로 매도세 지속</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13996,10 +14296,10 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="7" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14050,14 +14350,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>(전일) (포털·핀테크 플랫폼) 페이페이 결제액 34.9% 성장 등 실적 호조 지속</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14106,19 +14406,19 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="7" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>(전일) (비철금속 제련·금은동 광업) 금·구리 급등에 상장 이래 최고가 경신</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14166,10 +14466,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="7" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>(해운 3사, 컨테이너·벌크) 벌크운임 반등에 해운주 동반 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14216,14 +14520,14 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="7" t="inlineStr">
+      <c r="N10" s="10" t="inlineStr">
         <is>
           <t>(전일) (전력·원전 운영) 기업용 전기요금 10~15% 인상 발표로 실적 개선 기대</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14272,15 +14576,15 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="7" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14324,15 +14628,19 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="7" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>(증권·은행 겸영 금융지주) 금리 상승 수혜 기대에 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14380,10 +14688,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N13" s="7" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>(해운 3사, 컨테이너·벌크) 벌크운임 반등에 해운주 동반 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14434,15 +14746,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N14" s="7" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14484,7 +14796,11 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="7" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>(자동차 부품, 점화플러그) 특별한 뉴스 없음, 자동차·소비주 약세 동반</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N15"/>
@@ -14590,12 +14906,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14639,10 +14955,14 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="7" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>(중국 최대 금·구리 광산업체) 금·구리 동반 강세에 광산주 급등</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14691,10 +15011,10 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="7" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14741,10 +15061,10 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="7" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14791,14 +15111,14 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="7" t="inlineStr">
-        <is>
-          <t>(전일) (금광 채굴) 미 재무부 국채 바이백 확대에 금리 급락, 금값 급등</t>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>(쯔진광업의 금 사업 자회사) 금값 랠리에 모기업 후광 업고 급등</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14851,14 +15171,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="7" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>(전일) (제약) 상반기 매출 1.9%·조정순이익 12.7% 감소로 업종과 반대로 급락</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14911,19 +15231,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>(전일) 코스코해운홀딩스(컨테이너 해운): 특별한 뉴스 없음(호르무즈발 운임 강세 지속 추정)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14963,15 +15283,19 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="7" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>(홍콩 지하철 운영·역세권 개발) 특별한 뉴스 없음, 홍콩 강세장 속 고배당 수급 추정</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15017,15 +15341,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="7" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>(홍콩 최대 전력회사) 특별한 뉴스 없음, 홍콩 강세장 속 고배당 수급 추정</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15071,10 +15399,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N10" s="7" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>(라부부 등 아트토이 제조·유통) 상반기 이익 성장 둔화 시사에 급락</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15119,14 +15451,14 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="7" t="inlineStr">
-        <is>
-          <t>(전일) (금광 채굴) 금값 급등에 금광주 일제히 강세</t>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>(중국 대표 금광업체) 금값 4,600달러선 회복에 금광주 동반 급등</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15169,15 +15501,15 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="7" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15217,10 +15549,14 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="7" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>(마카오 카지노·리조트) 여름 성수기 마카오 매출 회복 기대에 강세</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15267,14 +15603,14 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="7" t="inlineStr">
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>(전일) 스와이어프로퍼티스(홍콩 상업용 부동산): 씨티의 홍콩 소매경기 하반기 개선 전망 보고서</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15319,10 +15655,10 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="7" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15371,14 +15707,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N16" s="7" t="inlineStr">
+      <c r="N16" s="10" t="inlineStr">
         <is>
           <t>(전일) SITC인터내셔널(아시아 역내 컨테이너 해운): 개별 뉴스 없음, 중간실적 앞둔 해운 강세 동조 추정</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15427,15 +15763,15 @@
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" s="7" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15481,10 +15817,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N18" s="7" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15535,10 +15871,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N19" s="7" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15585,10 +15921,14 @@
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" s="7" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr">
+        <is>
+          <t>(금광 채굴업체) 금값 3개월래 최고 랠리에 금광주 급등세 지속</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15639,19 +15979,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N21" s="7" t="inlineStr">
+      <c r="N21" s="10" t="inlineStr">
         <is>
           <t>(전일) (금광 채굴) 금값 급등과 실적 호조 여진으로 52주 신고가</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15691,10 +16031,14 @@
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" s="7" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr">
+        <is>
+          <t>(동남아 중심 물류·택배) 특별한 뉴스 없음, 홍콩 증시 전반 강세 동반 추정</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15743,7 +16087,7 @@
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" s="7" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N23"/>
@@ -15849,12 +16193,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15894,10 +16238,14 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="7" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>(중국 최대 국영 석유회사) 국제유가 한 달래 최고치 반등에 석유주 강세</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -15946,14 +16294,14 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="7" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>(전일) (AI 반도체 설계) 특별한 호재 부재, 차익실현과 수급 이탈 추정</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15998,19 +16346,19 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) 중신은행(전국구 주식제 상업은행): 테크주 급락 자금이 저평가 고배당 은행으로 이동</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16054,10 +16402,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>(휴머노이드 로봇 제조사, 8월 19일 상장) 상장 이틀 만에 차익매물로 급락</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16110,14 +16462,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>(전일) 코스코해운지주 A주(중국 최대 국영 컨테이너 해운): 호르무즈 운임 급등·머스크 가이던스 상향에 해운주 동반 급등</t>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>(중국 최대 컨테이너 해운사) 유럽항로 운임 급등에 해운주 강세</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16170,14 +16522,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>(전일) (지방은행) 상반기 실적발표를 앞두고 고배당·안전자산 선호 매수</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16228,10 +16580,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N8" s="7" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -16280,19 +16632,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="7" t="inlineStr">
+      <c r="N9" s="10" t="inlineStr">
         <is>
           <t>(전일) 화뎬신에너지(화뎬그룹 산하 신재생 발전사): 특별한 뉴스 없음(신재생 발전주 약세 흐름 속 신저가)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16336,10 +16688,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N10" s="7" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>(신재생에너지 발전 자회사) 특별한 뉴스 없음, 전력 유틸리티 업종 약세 동반</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16386,14 +16742,14 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="7" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>(전일) (금광 채굴) 미 국채금리 하락발 금값 급등에 대표 금광주로 매수 집중</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16442,10 +16798,10 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="7" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16494,14 +16850,14 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="7" t="inlineStr">
+      <c r="N13" s="10" t="inlineStr">
         <is>
           <t>(전일) 상하이은행(도시상업은행): 은행·배당 ETF 자금 유입 지속, 방어주 로테이션에 사상 최고가</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16548,15 +16904,15 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="7" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16602,15 +16958,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N15" s="7" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>(중형 증권사) 특별한 뉴스 없음, 증권업종 혼조 속 개별 수급 이탈 추정</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16656,10 +17016,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N16" s="7" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>(대형 화력발전 공기업) 특별한 뉴스 없음, 전력·배당주 전반 약세 동반</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16706,19 +17070,19 @@
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" s="7" t="inlineStr">
-        <is>
-          <t>(전일) (금광 채굴) 미 국채 바이백발 금리 급락에 금값 급등, 귀금속주 강세</t>
+      <c r="N17" s="10" t="inlineStr">
+        <is>
+          <t>(금광 채굴기업) 금값 4,600달러선 회복에 안전자산 수요 몰려 급등</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16764,10 +17128,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N18" s="7" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr">
+        <is>
+          <t>(정유·화학 대기업) 국제유가 한 달래 최고치 반등에 석유화학주 동반 강세</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -16818,7 +17186,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N19" s="7" t="inlineStr">
+      <c r="N19" s="10" t="inlineStr">
         <is>
           <t>(전일) 중국동방항공(항공 운송): 국제유가 상승에 따른 항공유 비용 부담과 시장 약세 동반</t>
         </is>

--- a/신고신저가_20260824.xlsx
+++ b/신고신저가_20260824.xlsx
@@ -8251,11 +8251,7 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="10" t="inlineStr">
-        <is>
-          <t>(페루·멕시코 구리광산) 구리 강세 랠리와 2분기 실적 서프라이즈에 신고가</t>
-        </is>
-      </c>
+      <c r="N9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -8741,11 +8737,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N18" s="10" t="inlineStr">
-        <is>
-          <t>(글로벌 구리광산 대형주) 구리 재고 타이트·AI 전력수요 기대에 신고가</t>
-        </is>
-      </c>
+      <c r="N18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -8961,11 +8953,7 @@
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" s="10" t="inlineStr">
-        <is>
-          <t>(전력 규제 유틸리티) 금리 상승기 고배당 유틸리티 동반 하락</t>
-        </is>
-      </c>
+      <c r="N22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -9651,11 +9639,7 @@
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" s="10" t="inlineStr">
-        <is>
-          <t>(전력 규제 유틸리티) 국채금리 상승 압력에 유틸리티 섹터 전반 신저가</t>
-        </is>
-      </c>
+      <c r="N35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -9867,11 +9851,7 @@
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" s="10" t="inlineStr">
-        <is>
-          <t>(전력·가스 규제 유틸리티) 장기 국채금리 고공행진에 금리민감주 동반 신저가</t>
-        </is>
-      </c>
+      <c r="N39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -10087,11 +10067,7 @@
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" s="10" t="inlineStr">
-        <is>
-          <t>(전력 규제 유틸리티) 장기금리 상승으로 배당주 매력 훼손, 매도 압력</t>
-        </is>
-      </c>
+      <c r="N43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -10147,11 +10123,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N44" s="10" t="inlineStr">
-        <is>
-          <t>(생명과학 분석장비) 뚜렷한 촉매 없이 실적 앞둔 매수세로 52주 고가 돌파</t>
-        </is>
-      </c>
+      <c r="N44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -10367,11 +10339,7 @@
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" s="10" t="inlineStr">
-        <is>
-          <t>(프레스티지 화장품) 분기 EPS 서프라이즈와 중국 매출 회복에 목표가 줄상향</t>
-        </is>
-      </c>
+      <c r="N48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -10479,11 +10447,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N50" s="10" t="inlineStr">
-        <is>
-          <t>(전력·가스 규제 유틸리티) 국채수익률 고점권 유지에 금리민감주 매도</t>
-        </is>
-      </c>
+      <c r="N50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -12569,11 +12533,7 @@
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
-      <c r="N89" s="10" t="inlineStr">
-        <is>
-          <t>(저가 잡화 소매체인) 실적 발표를 앞둔 매수세와 목표가 상향</t>
-        </is>
-      </c>
+      <c r="N89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
@@ -12785,7 +12745,7 @@
       <c r="M93" t="inlineStr"/>
       <c r="N93" s="10" t="inlineStr">
         <is>
-          <t>(AI 정밀의료 유전체분석) 흑색종 임상 성공 후광과 자체 가이던스 상향 랠리</t>
+          <t>(전일) (AI 정밀의료 데이터분석) 특별한 뉴스 없음, AI헬스케어 순환매 유입 추정</t>
         </is>
       </c>
     </row>
@@ -13275,11 +13235,7 @@
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
-      <c r="N102" s="10" t="inlineStr">
-        <is>
-          <t>(캐나다계 금광 채굴) 금값 3개월래 최고치 랠리와 CIBC 투자의견 상향</t>
-        </is>
-      </c>
+      <c r="N102" s="10" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
@@ -13751,11 +13707,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N111" s="10" t="inlineStr">
-        <is>
-          <t>(전자시장조성 트레이딩) 브로커리지 부문 35~40억달러 매각 검토설에 급등</t>
-        </is>
-      </c>
+      <c r="N111" s="10" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
@@ -14072,11 +14024,7 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="10" t="inlineStr">
-        <is>
-          <t>(유니클로 운영 의류업체) 미국 대형 유통 실적 부진 여파로 소비주 동반 급락</t>
-        </is>
-      </c>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -14130,11 +14078,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="10" t="inlineStr">
-        <is>
-          <t>(일본 통신 1위 NTT그룹) 방어주 선호 속 매수세로 신고가</t>
-        </is>
-      </c>
+      <c r="N3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -14242,11 +14186,7 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="10" t="inlineStr">
-        <is>
-          <t>(공조기기 세계 1위) 8월 초 분기 실적 부진의 여진으로 매도세 지속</t>
-        </is>
-      </c>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -14466,11 +14406,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="10" t="inlineStr">
-        <is>
-          <t>(해운 3사, 컨테이너·벌크) 벌크운임 반등에 해운주 동반 신고가</t>
-        </is>
-      </c>
+      <c r="N9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -14628,11 +14564,7 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="10" t="inlineStr">
-        <is>
-          <t>(증권·은행 겸영 금융지주) 금리 상승 수혜 기대에 신고가</t>
-        </is>
-      </c>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -14688,11 +14620,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N13" s="10" t="inlineStr">
-        <is>
-          <t>(해운 3사, 컨테이너·벌크) 벌크운임 반등에 해운주 동반 신고가</t>
-        </is>
-      </c>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -14796,11 +14724,7 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="10" t="inlineStr">
-        <is>
-          <t>(자동차 부품, 점화플러그) 특별한 뉴스 없음, 자동차·소비주 약세 동반</t>
-        </is>
-      </c>
+      <c r="N15" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N15"/>
@@ -14955,11 +14879,7 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="10" t="inlineStr">
-        <is>
-          <t>(중국 최대 금·구리 광산업체) 금·구리 동반 강세에 광산주 급등</t>
-        </is>
-      </c>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -15113,7 +15033,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" s="10" t="inlineStr">
         <is>
-          <t>(쯔진광업의 금 사업 자회사) 금값 랠리에 모기업 후광 업고 급등</t>
+          <t>(전일) (금광 채굴) 미 재무부 국채 바이백 확대에 금리 급락, 금값 급등</t>
         </is>
       </c>
     </row>
@@ -15283,11 +15203,7 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="10" t="inlineStr">
-        <is>
-          <t>(홍콩 지하철 운영·역세권 개발) 특별한 뉴스 없음, 홍콩 강세장 속 고배당 수급 추정</t>
-        </is>
-      </c>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -15341,11 +15257,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="10" t="inlineStr">
-        <is>
-          <t>(홍콩 최대 전력회사) 특별한 뉴스 없음, 홍콩 강세장 속 고배당 수급 추정</t>
-        </is>
-      </c>
+      <c r="N9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -15399,11 +15311,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N10" s="10" t="inlineStr">
-        <is>
-          <t>(라부부 등 아트토이 제조·유통) 상반기 이익 성장 둔화 시사에 급락</t>
-        </is>
-      </c>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -15453,7 +15361,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" s="10" t="inlineStr">
         <is>
-          <t>(중국 대표 금광업체) 금값 4,600달러선 회복에 금광주 동반 급등</t>
+          <t>(전일) (금광 채굴) 금값 급등에 금광주 일제히 강세</t>
         </is>
       </c>
     </row>
@@ -15549,11 +15457,7 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="10" t="inlineStr">
-        <is>
-          <t>(마카오 카지노·리조트) 여름 성수기 마카오 매출 회복 기대에 강세</t>
-        </is>
-      </c>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -15921,11 +15825,7 @@
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" s="10" t="inlineStr">
-        <is>
-          <t>(금광 채굴업체) 금값 3개월래 최고 랠리에 금광주 급등세 지속</t>
-        </is>
-      </c>
+      <c r="N20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -16031,11 +15931,7 @@
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" s="10" t="inlineStr">
-        <is>
-          <t>(동남아 중심 물류·택배) 특별한 뉴스 없음, 홍콩 증시 전반 강세 동반 추정</t>
-        </is>
-      </c>
+      <c r="N22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -16238,11 +16134,7 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="10" t="inlineStr">
-        <is>
-          <t>(중국 최대 국영 석유회사) 국제유가 한 달래 최고치 반등에 석유주 강세</t>
-        </is>
-      </c>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -16402,11 +16294,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="10" t="inlineStr">
-        <is>
-          <t>(휴머노이드 로봇 제조사, 8월 19일 상장) 상장 이틀 만에 차익매물로 급락</t>
-        </is>
-      </c>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -16464,7 +16352,7 @@
       </c>
       <c r="N6" s="10" t="inlineStr">
         <is>
-          <t>(중국 최대 컨테이너 해운사) 유럽항로 운임 급등에 해운주 강세</t>
+          <t>(전일) 코스코해운지주 A주(중국 최대 국영 컨테이너 해운): 호르무즈 운임 급등·머스크 가이던스 상향에 해운주 동반 급등</t>
         </is>
       </c>
     </row>
@@ -16688,11 +16576,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N10" s="10" t="inlineStr">
-        <is>
-          <t>(신재생에너지 발전 자회사) 특별한 뉴스 없음, 전력 유틸리티 업종 약세 동반</t>
-        </is>
-      </c>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -16958,11 +16842,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N15" s="10" t="inlineStr">
-        <is>
-          <t>(중형 증권사) 특별한 뉴스 없음, 증권업종 혼조 속 개별 수급 이탈 추정</t>
-        </is>
-      </c>
+      <c r="N15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -17016,11 +16896,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N16" s="10" t="inlineStr">
-        <is>
-          <t>(대형 화력발전 공기업) 특별한 뉴스 없음, 전력·배당주 전반 약세 동반</t>
-        </is>
-      </c>
+      <c r="N16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -17072,7 +16948,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" s="10" t="inlineStr">
         <is>
-          <t>(금광 채굴기업) 금값 4,600달러선 회복에 안전자산 수요 몰려 급등</t>
+          <t>(전일) (금광 채굴) 미 국채 바이백발 금리 급락에 금값 급등, 귀금속주 강세</t>
         </is>
       </c>
     </row>
@@ -17128,11 +17004,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N18" s="10" t="inlineStr">
-        <is>
-          <t>(정유·화학 대기업) 국제유가 한 달래 최고치 반등에 석유화학주 동반 강세</t>
-        </is>
-      </c>
+      <c r="N18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">

--- a/신고신저가_20260824.xlsx
+++ b/신고신저가_20260824.xlsx
@@ -8251,7 +8251,11 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="10" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>(페루·멕시코 구리광산) 구리 강세 랠리와 2분기 실적 서프라이즈에 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -8737,7 +8741,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N18" s="10" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr">
+        <is>
+          <t>(글로벌 구리광산 대형주) 구리 재고 타이트·AI 전력수요 기대에 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -8953,7 +8961,11 @@
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" s="10" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr">
+        <is>
+          <t>(전력 규제 유틸리티) 금리 상승기 고배당 유틸리티 동반 하락</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -9639,7 +9651,11 @@
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" s="10" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr">
+        <is>
+          <t>(전력 규제 유틸리티) 국채금리 상승 압력에 유틸리티 섹터 전반 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -9851,7 +9867,11 @@
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" s="10" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr">
+        <is>
+          <t>(전력·가스 규제 유틸리티) 장기 국채금리 고공행진에 금리민감주 동반 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -10067,7 +10087,11 @@
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" s="10" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr">
+        <is>
+          <t>(전력 규제 유틸리티) 장기금리 상승으로 배당주 매력 훼손, 매도 압력</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -10123,7 +10147,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N44" s="10" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr">
+        <is>
+          <t>(생명과학 분석장비) 뚜렷한 촉매 없이 실적 앞둔 매수세로 52주 고가 돌파</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -10339,7 +10367,11 @@
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" s="10" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr">
+        <is>
+          <t>(프레스티지 화장품) 분기 EPS 서프라이즈와 중국 매출 회복에 목표가 줄상향</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -10447,7 +10479,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N50" s="10" t="inlineStr"/>
+      <c r="N50" s="10" t="inlineStr">
+        <is>
+          <t>(전력·가스 규제 유틸리티) 국채수익률 고점권 유지에 금리민감주 매도</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -12533,7 +12569,11 @@
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
-      <c r="N89" s="10" t="inlineStr"/>
+      <c r="N89" s="10" t="inlineStr">
+        <is>
+          <t>(저가 잡화 소매체인) 실적 발표를 앞둔 매수세와 목표가 상향</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
@@ -12745,7 +12785,7 @@
       <c r="M93" t="inlineStr"/>
       <c r="N93" s="10" t="inlineStr">
         <is>
-          <t>(전일) (AI 정밀의료 데이터분석) 특별한 뉴스 없음, AI헬스케어 순환매 유입 추정</t>
+          <t>(AI 정밀의료 유전체분석) 흑색종 임상 성공 후광과 자체 가이던스 상향 랠리</t>
         </is>
       </c>
     </row>
@@ -13235,7 +13275,11 @@
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
-      <c r="N102" s="10" t="inlineStr"/>
+      <c r="N102" s="10" t="inlineStr">
+        <is>
+          <t>(캐나다계 금광 채굴) 금값 3개월래 최고치 랠리와 CIBC 투자의견 상향</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
@@ -13707,7 +13751,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N111" s="10" t="inlineStr"/>
+      <c r="N111" s="10" t="inlineStr">
+        <is>
+          <t>(전자시장조성 트레이딩) 브로커리지 부문 35~40억달러 매각 검토설에 급등</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
@@ -14024,7 +14072,11 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="10" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>(유니클로 운영 의류업체) 미국 대형 유통 실적 부진 여파로 소비주 동반 급락</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -14078,7 +14130,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="10" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>(일본 통신 1위 NTT그룹) 방어주 선호 속 매수세로 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -14186,7 +14242,11 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="10" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>(공조기기 세계 1위) 8월 초 분기 실적 부진의 여진으로 매도세 지속</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -14406,7 +14466,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="10" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>(해운 3사, 컨테이너·벌크) 벌크운임 반등에 해운주 동반 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -14564,7 +14628,11 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="10" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>(증권·은행 겸영 금융지주) 금리 상승 수혜 기대에 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -14620,7 +14688,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N13" s="10" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>(해운 3사, 컨테이너·벌크) 벌크운임 반등에 해운주 동반 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -14724,7 +14796,11 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="10" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>(자동차 부품, 점화플러그) 특별한 뉴스 없음, 자동차·소비주 약세 동반</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N15"/>
@@ -14879,7 +14955,11 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="10" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>(중국 최대 금·구리 광산업체) 금·구리 동반 강세에 광산주 급등</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -15033,7 +15113,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" s="10" t="inlineStr">
         <is>
-          <t>(전일) (금광 채굴) 미 재무부 국채 바이백 확대에 금리 급락, 금값 급등</t>
+          <t>(쯔진광업의 금 사업 자회사) 금값 랠리에 모기업 후광 업고 급등</t>
         </is>
       </c>
     </row>
@@ -15203,7 +15283,11 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="10" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>(홍콩 지하철 운영·역세권 개발) 특별한 뉴스 없음, 홍콩 강세장 속 고배당 수급 추정</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -15257,7 +15341,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="10" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>(홍콩 최대 전력회사) 특별한 뉴스 없음, 홍콩 강세장 속 고배당 수급 추정</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -15311,7 +15399,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N10" s="10" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>(라부부 등 아트토이 제조·유통) 상반기 이익 성장 둔화 시사에 급락</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -15361,7 +15453,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" s="10" t="inlineStr">
         <is>
-          <t>(전일) (금광 채굴) 금값 급등에 금광주 일제히 강세</t>
+          <t>(중국 대표 금광업체) 금값 4,600달러선 회복에 금광주 동반 급등</t>
         </is>
       </c>
     </row>
@@ -15457,7 +15549,11 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="10" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>(마카오 카지노·리조트) 여름 성수기 마카오 매출 회복 기대에 강세</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -15825,7 +15921,11 @@
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" s="10" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr">
+        <is>
+          <t>(금광 채굴업체) 금값 3개월래 최고 랠리에 금광주 급등세 지속</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -15931,7 +16031,11 @@
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" s="10" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr">
+        <is>
+          <t>(동남아 중심 물류·택배) 특별한 뉴스 없음, 홍콩 증시 전반 강세 동반 추정</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -16134,7 +16238,11 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="10" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>(중국 최대 국영 석유회사) 국제유가 한 달래 최고치 반등에 석유주 강세</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -16294,7 +16402,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="10" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>(휴머노이드 로봇 제조사, 8월 19일 상장) 상장 이틀 만에 차익매물로 급락</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -16352,7 +16464,7 @@
       </c>
       <c r="N6" s="10" t="inlineStr">
         <is>
-          <t>(전일) 코스코해운지주 A주(중국 최대 국영 컨테이너 해운): 호르무즈 운임 급등·머스크 가이던스 상향에 해운주 동반 급등</t>
+          <t>(중국 최대 컨테이너 해운사) 유럽항로 운임 급등에 해운주 강세</t>
         </is>
       </c>
     </row>
@@ -16576,7 +16688,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N10" s="10" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>(신재생에너지 발전 자회사) 특별한 뉴스 없음, 전력 유틸리티 업종 약세 동반</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -16842,7 +16958,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N15" s="10" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>(중형 증권사) 특별한 뉴스 없음, 증권업종 혼조 속 개별 수급 이탈 추정</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -16896,7 +17016,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N16" s="10" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>(대형 화력발전 공기업) 특별한 뉴스 없음, 전력·배당주 전반 약세 동반</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -16948,7 +17072,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" s="10" t="inlineStr">
         <is>
-          <t>(전일) (금광 채굴) 미 국채 바이백발 금리 급락에 금값 급등, 귀금속주 강세</t>
+          <t>(금광 채굴기업) 금값 4,600달러선 회복에 안전자산 수요 몰려 급등</t>
         </is>
       </c>
     </row>
@@ -17004,7 +17128,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N18" s="10" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr">
+        <is>
+          <t>(정유·화학 대기업) 국제유가 한 달래 최고치 반등에 석유화학주 동반 강세</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">

--- a/신고신저가_20260824.xlsx
+++ b/신고신저가_20260824.xlsx
@@ -618,7 +618,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>💬 ■ 결론: 금요일 시장을 관통한 것은 미 재무부의 장기국채 바이백 확대와 국가부채 40조달러 돌파였다. 달러가 밀리고 금이 3개월래 최고인 온스당 4,608달러로 올라서면서 금·구리 광산주가 미국과 중화권에서 동시에 신고가를 냈고, 같은 힘이 반대편에서는 장기금리를 4.7%대에 붙들어 미국 규제 유틸리티 14종을 무더기 신저가로 밀어냈다. 지수는 조용했지만 그 아래에서는 실물자산과 채권 대용물이 정면으로 갈렸다.</t>
+          <t>💬 ■ 결론: 금요일 시장을 관통한 것은 미 재무부의 장기국채 바이백 확대와 국가부채 40조달러 돌파였다. 달러가 밀리고 금이 사상 최고인 온스당 4,600달러 선으로 올라서면서 금·구리 광산주가 미국과 중화권에서 동시에 신고가를 냈고, 같은 힘이 반대편에서는 장기금리를 4.7%대에 붙들어 미국 규제 유틸리티 14종을 무더기 신저가로 밀어냈다. 지수는 조용했지만 그 아래에서는 실물자산과 채권 대용물이 정면으로 갈렸다.</t>
         </is>
       </c>
     </row>
